--- a/export/n_r_5_n/v1.xlsx
+++ b/export/n_r_5_n/v1.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>09/2022</t>
+          <t>9/22</t>
         </is>
       </c>
     </row>
@@ -613,7 +613,7 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>1/9/22</t>
+          <t>1/9/2022</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
@@ -645,7 +645,7 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>2/9/22</t>
+          <t>2/9/2022</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
@@ -673,7 +673,7 @@
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>3/9/22</t>
+          <t>3/9/2022</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
@@ -689,7 +689,7 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>4/9/22</t>
+          <t>4/9/2022</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
@@ -721,7 +721,7 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>5/9/22</t>
+          <t>5/9/2022</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
@@ -749,7 +749,7 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>6/9/22</t>
+          <t>6/9/2022</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
@@ -777,7 +777,7 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>7/9/22</t>
+          <t>7/9/2022</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
@@ -805,7 +805,7 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>8/9/22</t>
+          <t>8/9/2022</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
@@ -833,7 +833,7 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>9/9/22</t>
+          <t>9/9/2022</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
@@ -861,7 +861,7 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>10/9/22</t>
+          <t>10/9/2022</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
@@ -877,7 +877,7 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>11/9/22</t>
+          <t>11/9/2022</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
@@ -905,7 +905,7 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>12/9/22</t>
+          <t>12/9/2022</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
@@ -933,7 +933,7 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>13/9/22</t>
+          <t>13/9/2022</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
@@ -965,7 +965,7 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>14/9/22</t>
+          <t>14/9/2022</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
@@ -993,7 +993,7 @@
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>15/9/22</t>
+          <t>15/9/2022</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
@@ -1021,7 +1021,7 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>16/9/22</t>
+          <t>16/9/2022</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
@@ -1049,7 +1049,7 @@
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>17/9/22</t>
+          <t>17/9/2022</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
@@ -1065,7 +1065,7 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>18/9/22</t>
+          <t>18/9/2022</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
@@ -1097,7 +1097,7 @@
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>19/9/22</t>
+          <t>19/9/2022</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
@@ -1125,7 +1125,7 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>20/9/22</t>
+          <t>20/9/2022</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
